--- a/data/trans_dic/P21D_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,32</t>
+          <t>0,03; 0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,23</t>
+          <t>0,02; 0,2</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3838</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1111</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4246</t>
+          <t>0; 4296</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3974</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4018</t>
+          <t>0; 4889</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1291</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1577</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1834</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4243</t>
+          <t>0; 4222</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3900</t>
+          <t>0; 4247</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4574</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>521; 5175</t>
+          <t>558; 5563</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>744; 7418</t>
+          <t>614; 6434</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Habitat-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,35</t>
+          <t>0,03; 0,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 3845</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>0; 4541</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3816</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>0; 4205</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 3957</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 4712</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 4551</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558; 5563</t>
+          <t>564; 5521</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>614; 6434</t>
+          <t>705; 6677</t>
         </is>
       </c>
     </row>
